--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21F47D9-0F7C-F749-A91F-AB4A83CDA267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32F692C-B1F0-F344-98E2-742B02830F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20940" yWindow="-15300" windowWidth="28040" windowHeight="14560" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
+    <workbookView xWindow="1160" yWindow="4540" windowWidth="27020" windowHeight="11060" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Allied Able 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>brand</t>
   </si>
@@ -59,12 +59,6 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -210,6 +204,117 @@
   </si>
   <si>
     <t>a10:g34</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>BSA 68</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
@@ -219,7 +324,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -336,6 +441,18 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -363,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -394,6 +511,13 @@
     <xf numFmtId="1" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,8 +641,8 @@
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1104900</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
@@ -873,34 +997,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299AF885-3999-4E4F-8F92-5857EF0F7F08}">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:AH45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
-    <col min="10" max="24" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="28" width="16" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -908,7 +1030,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -916,49 +1038,182 @@
         <v>45855</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" s="30" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="N6" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="U6" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="X6" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z6" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA6" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB6" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF6" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG6" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH6" s="31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>57</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="1">
+        <v>50</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>6775</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="21" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="21" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="14">
         <v>52</v>
@@ -985,12 +1240,12 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" ht="21" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="16">
         <v>540</v>
@@ -1017,12 +1272,12 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" ht="21" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="16">
         <v>390</v>
@@ -1049,12 +1304,12 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" ht="21" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="16">
         <v>460</v>
@@ -1081,12 +1336,12 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" ht="21" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="16">
         <v>70.5</v>
@@ -1113,12 +1368,12 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" ht="21" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="16">
         <v>75</v>
@@ -1145,12 +1400,12 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" ht="21" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="16">
         <v>80</v>
@@ -1179,10 +1434,10 @@
     </row>
     <row r="17" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="16">
         <v>435</v>
@@ -1211,10 +1466,10 @@
     </row>
     <row r="18" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="16">
         <v>410</v>
@@ -1244,10 +1499,10 @@
     </row>
     <row r="19" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="16">
         <v>534</v>
@@ -1277,10 +1532,10 @@
     </row>
     <row r="20" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C20" s="16">
         <v>97</v>
@@ -1310,10 +1565,10 @@
     </row>
     <row r="21" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="16">
         <v>1039</v>
@@ -1343,10 +1598,10 @@
     </row>
     <row r="22" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="16">
         <v>752</v>
@@ -1376,10 +1631,10 @@
     </row>
     <row r="23" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" s="16">
         <v>55</v>
@@ -1409,10 +1664,10 @@
     </row>
     <row r="24" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" s="16">
         <v>611</v>
@@ -1442,7 +1697,7 @@
     </row>
     <row r="25" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="16"/>
@@ -1463,10 +1718,10 @@
     </row>
     <row r="26" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="16">
         <v>900</v>
@@ -1496,10 +1751,10 @@
     </row>
     <row r="27" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C27" s="20">
         <v>165</v>
@@ -1529,10 +1784,10 @@
     </row>
     <row r="28" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C28" s="20">
         <v>40</v>
@@ -1562,10 +1817,10 @@
     </row>
     <row r="29" spans="1:18" ht="21" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C29" s="20">
         <v>80</v>
@@ -1595,7 +1850,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18">
@@ -1627,7 +1882,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18">
@@ -1659,7 +1914,7 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18">
@@ -1691,7 +1946,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="18"/>
       <c r="J33" s="28"/>
@@ -1706,7 +1961,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFB1B84-45F2-2F46-B7A3-249760CB47E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF5A4CF-3A5D-FD43-8FBB-4F584D85BFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -1347,9 +1347,6 @@
       <c r="A43" t="s">
         <v>72</v>
       </c>
-      <c r="B43" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF5A4CF-3A5D-FD43-8FBB-4F584D85BFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E41FE-8AF2-3245-841F-82CBE23F2AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9560" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -46,9 +46,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://alliedcycleworks.com/products/able-frameset-custom?srsltid=AfmBOoqHGwuU49K3fUnbLhGvnC72JxoDhf7hq2QSozXRaGzVgJpCY19L</t>
-  </si>
-  <si>
     <t>17-Jul-2025</t>
   </si>
   <si>
@@ -377,6 +374,12 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://alliedcycleworks.com/collections/able</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0252/9997/6243/files/ABLE_Fireball_20040_1.jpg?v=1743972443</t>
   </si>
 </sst>
 </file>
@@ -743,7 +746,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -751,46 +754,51 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
       </c>
       <c r="C9">
         <v>540</v>
@@ -810,10 +818,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
       </c>
       <c r="C10">
         <v>390</v>
@@ -833,10 +841,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11">
         <v>460</v>
@@ -856,10 +864,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
       </c>
       <c r="C12">
         <v>70.5</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -902,10 +910,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
       </c>
       <c r="C14">
         <v>80</v>
@@ -925,10 +933,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
       </c>
       <c r="C15">
         <v>435</v>
@@ -948,10 +956,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
       </c>
       <c r="C16">
         <v>410</v>
@@ -971,10 +979,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
       </c>
       <c r="C17">
         <v>534</v>
@@ -994,10 +1002,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
       </c>
       <c r="C18">
         <v>97</v>
@@ -1017,10 +1025,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
       </c>
       <c r="C19">
         <v>1039</v>
@@ -1040,10 +1048,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
       </c>
       <c r="C20">
         <v>752</v>
@@ -1063,10 +1071,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
       </c>
       <c r="C21">
         <v>55</v>
@@ -1086,10 +1094,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>46</v>
       </c>
       <c r="C22">
         <v>611</v>
@@ -1109,15 +1117,15 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
         <v>48</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
       </c>
       <c r="C24">
         <v>900</v>
@@ -1137,10 +1145,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
         <v>50</v>
-      </c>
-      <c r="B25" t="s">
-        <v>51</v>
       </c>
       <c r="C25">
         <v>165</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
         <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
       </c>
       <c r="C26">
         <v>40</v>
@@ -1183,10 +1191,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
         <v>54</v>
-      </c>
-      <c r="B27" t="s">
-        <v>55</v>
       </c>
       <c r="C27">
         <v>80</v>
@@ -1206,7 +1214,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>700</v>
@@ -1226,7 +1234,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>57</v>
@@ -1246,7 +1254,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>57</v>
@@ -1266,267 +1274,267 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
         <v>61</v>
-      </c>
-      <c r="B34" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
         <v>113</v>
-      </c>
-      <c r="B35" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
         <v>115</v>
-      </c>
-      <c r="B36" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
         <v>117</v>
-      </c>
-      <c r="B37" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
         <v>63</v>
-      </c>
-      <c r="B38" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
         <v>65</v>
-      </c>
-      <c r="B39" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s">
         <v>67</v>
-      </c>
-      <c r="B40" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
         <v>69</v>
-      </c>
-      <c r="B41" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" t="s">
         <v>77</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" t="s">
         <v>79</v>
-      </c>
-      <c r="B48" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
         <v>81</v>
-      </c>
-      <c r="B49" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" t="s">
         <v>84</v>
-      </c>
-      <c r="B51" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" t="s">
         <v>87</v>
-      </c>
-      <c r="B53" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" t="s">
         <v>93</v>
-      </c>
-      <c r="B58" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" t="s">
         <v>98</v>
-      </c>
-      <c r="B62" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>105</v>
+      </c>
+      <c r="B69" t="s">
         <v>106</v>
-      </c>
-      <c r="B69" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" t="s">
         <v>108</v>
-      </c>
-      <c r="B70" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" t="s">
         <v>111</v>
-      </c>
-      <c r="B72" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E41FE-8AF2-3245-841F-82CBE23F2AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28189281-D433-0E48-8FB6-616F953455B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9560" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8180" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -355,9 +355,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -380,17 +377,32 @@
   </si>
   <si>
     <t>https://cdn.shopify.com/s/files/1/0252/9997/6243/files/ABLE_Fireball_20040_1.jpg?v=1743972443</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bentonville, Arkansas, USA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -413,8 +425,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -754,12 +767,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1292,26 +1305,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
         <v>112</v>
-      </c>
-      <c r="B35" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
         <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
         <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1533,8 +1546,16 @@
       <c r="A72" t="s">
         <v>110</v>
       </c>
-      <c r="B72" t="s">
-        <v>111</v>
+      <c r="B72" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28189281-D433-0E48-8FB6-616F953455B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79BA6E6-01B5-054A-8085-66D77698D39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8180" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>Bentonville, Arkansas, USA</t>
+  </si>
+  <si>
+    <t>https://nminus1bikes.substack.com/p/allied-able-gravel-bike-review</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +1403,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -1408,12 +1411,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>83</v>
       </c>
@@ -1421,7 +1424,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -1429,7 +1432,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>86</v>
       </c>
@@ -1437,27 +1440,27 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>92</v>
       </c>
@@ -1465,17 +1468,23 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>96</v>
       </c>
@@ -1483,7 +1492,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -1491,12 +1500,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79BA6E6-01B5-054A-8085-66D77698D39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A22D58-30B6-964C-89E8-5449B5441848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8180" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A22D58-30B6-964C-89E8-5449B5441848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DD627F-2134-5E45-A9DF-45987F4FAE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8180" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -389,6 +389,24 @@
   </si>
   <si>
     <t>https://nminus1bikes.substack.com/p/allied-able-gravel-bike-review</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -727,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1403,167 +1421,197 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>80</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B55" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>83</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B57" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>85</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B58" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>86</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B59" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>92</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B64" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C65" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>96</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B67" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>97</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B68" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>105</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B75" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>107</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B76" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>110</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>120</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>121</v>
       </c>
     </row>

--- a/data/gravel/Allied Able 2025.xlsx
+++ b/data/gravel/Allied Able 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DD627F-2134-5E45-A9DF-45987F4FAE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F27524-9671-6142-A4B5-5146971EA1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8180" yWindow="2060" windowWidth="20620" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,9 +154,6 @@
     <t>M. FORK RAKE</t>
   </si>
   <si>
-    <t>front_cent</t>
-  </si>
-  <si>
     <t>N. FRONT CENTER</t>
   </si>
   <si>
@@ -407,6 +404,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>front_center</t>
   </si>
 </sst>
 </file>
@@ -788,12 +788,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1127,11 +1127,11 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
       </c>
       <c r="C22">
         <v>611</v>
@@ -1151,15 +1151,15 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
       </c>
       <c r="C24">
         <v>900</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
       </c>
       <c r="C25">
         <v>165</v>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
         <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
       </c>
       <c r="C26">
         <v>40</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
         <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
       </c>
       <c r="C27">
         <v>80</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>700</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>57</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>57</v>
@@ -1308,311 +1308,311 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" t="s">
         <v>60</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
         <v>111</v>
-      </c>
-      <c r="B35" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
         <v>113</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
         <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
         <v>62</v>
-      </c>
-      <c r="B38" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" t="s">
         <v>64</v>
-      </c>
-      <c r="B39" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" t="s">
         <v>66</v>
-      </c>
-      <c r="B40" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" t="s">
         <v>68</v>
-      </c>
-      <c r="B41" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" t="s">
         <v>76</v>
-      </c>
-      <c r="B47" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" t="s">
         <v>78</v>
-      </c>
-      <c r="B48" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" t="s">
         <v>80</v>
-      </c>
-      <c r="B55" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" t="s">
         <v>83</v>
-      </c>
-      <c r="B57" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" t="s">
         <v>86</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" t="s">
         <v>92</v>
-      </c>
-      <c r="B64" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" t="s">
         <v>97</v>
-      </c>
-      <c r="B68" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" t="s">
         <v>105</v>
-      </c>
-      <c r="B75" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" t="s">
         <v>107</v>
-      </c>
-      <c r="B76" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>119</v>
+      </c>
+      <c r="B79" t="s">
         <v>120</v>
-      </c>
-      <c r="B79" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
